--- a/data/trans_orig/P15B_tráfico-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15B_tráfico-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25689</t>
+          <t>25741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27729</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39116</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>40417</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>75745</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>72517</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93001</t>
+          <t>93620</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>81071</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>143456</t>
+          <t>141138</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>169053</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>30401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>46960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,63%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>26339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>28229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>35945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>50595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>51902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29472</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>39882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77206</t>
+          <t>77876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89777</t>
+          <t>89908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45300</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>25110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44722</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50914</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61672</t>
+          <t>61624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>41295</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>53631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96462</t>
+          <t>96798</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112649</t>
+          <t>112355</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16448</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24263</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>27739</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41049</t>
+          <t>41237</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>59210</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89346</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61910</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102019</t>
+          <t>103161</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>141291</t>
+          <t>144262</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>197626</t>
+          <t>197917</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>227762</t>
+          <t>229550</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>193988</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>219489</t>
+          <t>219925</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>401086</t>
+          <t>398115</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>440358</t>
+          <t>439216</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26788</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21067</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31087</t>
+          <t>31071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21369</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35197</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>59937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71824</t>
+          <t>71301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>14836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>26462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>35518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49391</t>
+          <t>49041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61153</t>
+          <t>61109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>23162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>27823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42500</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>20082</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>31419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>24836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54380</t>
+          <t>54500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54840</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>61994</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>142929</t>
+          <t>141268</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>166326</t>
+          <t>166166</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147049</t>
+          <t>147234</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>167875</t>
+          <t>168338</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>296984</t>
+          <t>297485</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>328808</t>
+          <t>327229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29920</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24276</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>22305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>28239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39013</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27149</t>
+          <t>33394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46105</t>
+          <t>47518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30831</t>
+          <t>31916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34108</t>
+          <t>35238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>50811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57705</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>21660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22267</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>40990</t>
+          <t>42121</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>45728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48128</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25103</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26136</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>37332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,49%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,22 +12447,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17773</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,27 +12560,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>27774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>48258</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>44910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51160</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14512</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>36116</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>27734</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34539</t>
+          <t>43096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>46730</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44873</t>
+          <t>52100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>68838</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76833</t>
+          <t>92079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>114236</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>27384</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>39566</t>
+          <t>46638</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>40062</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44594</t>
+          <t>52735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>46168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70825</t>
+          <t>76711</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60207</t>
+          <t>66540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>110382</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81571</t>
+          <t>90501</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>121571</t>
+          <t>131372</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>160554</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128305</t>
+          <t>143200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>159605</t>
+          <t>173743</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>166630</t>
+          <t>181155</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>153396</t>
+          <t>165640</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>177633</t>
+          <t>193420</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>312534</t>
+          <t>341709</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>291162</t>
+          <t>320719</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>331162</t>
+          <t>361590</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
